--- a/r5-aist-trustworthyai-poc-pipeline/CodeSystem-EUAIActCodeSystem.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/CodeSystem-EUAIActCodeSystem.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="182">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Custom Codes</t>
+    <t>EU AI Transparency Custom Codes</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Central repository of legal and technical terms according to the EU AI Act.</t>
+    <t>Custom codes used in this IG to represent AI transparency, data-use, provenance, technical documentation, data-quality, and human-oversight documentation concepts.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -189,10 +189,22 @@
     <t>AI Transparency Information</t>
   </si>
   <si>
-    <t>informed-consent</t>
-  </si>
-  <si>
-    <t>Informed Consent</t>
+    <t>patient-information-provided</t>
+  </si>
+  <si>
+    <t>Patient Information Provided</t>
+  </si>
+  <si>
+    <t>patient-explanation-requested</t>
+  </si>
+  <si>
+    <t>Patient Explanation Requested</t>
+  </si>
+  <si>
+    <t>patient-explanation-provided</t>
+  </si>
+  <si>
+    <t>Patient Explanation Provided</t>
   </si>
   <si>
     <t>accuracy</t>
@@ -213,12 +225,48 @@
     <t>Specificity</t>
   </si>
   <si>
+    <t>robustness</t>
+  </si>
+  <si>
+    <t>Robustness</t>
+  </si>
+  <si>
+    <t>clinically-validated</t>
+  </si>
+  <si>
+    <t>Clinically Validated</t>
+  </si>
+  <si>
+    <t>The AI system has completed clinical validation.</t>
+  </si>
+  <si>
     <t>not-clinically-validated</t>
   </si>
   <si>
     <t>Not Clinically Validated</t>
   </si>
   <si>
+    <t>The AI system has not completed clinical validation.</t>
+  </si>
+  <si>
+    <t>validation-in-progress</t>
+  </si>
+  <si>
+    <t>Validation In Progress</t>
+  </si>
+  <si>
+    <t>Clinical validation is currently in progress.</t>
+  </si>
+  <si>
+    <t>technical-validation-only</t>
+  </si>
+  <si>
+    <t>Technical Validation Only</t>
+  </si>
+  <si>
+    <t>Only technical or syntactic validation has been performed.</t>
+  </si>
+  <si>
     <t>triage</t>
   </si>
   <si>
@@ -261,7 +309,7 @@
     <t>CE Mark</t>
   </si>
   <si>
-    <t>Indicates if the device has a CE mark.</t>
+    <t>Indicates whether the device has a CE mark.</t>
   </si>
   <si>
     <t>notified-body-id</t>
@@ -300,6 +348,15 @@
     <t>The intended target population.</t>
   </si>
   <si>
+    <t>eu-ai-database-id</t>
+  </si>
+  <si>
+    <t>EU AI Database Identifier</t>
+  </si>
+  <si>
+    <t>Identifier for an AI system registration in the EU AI database or an equivalent AI system registry.</t>
+  </si>
+  <si>
     <t>primary-use</t>
   </si>
   <si>
@@ -315,7 +372,7 @@
     <t>Secondary Use</t>
   </si>
   <si>
-    <t>Processing for research, AI training, or policy making.</t>
+    <t>Processing for research, AI training, policy making, or other permitted secondary-use purposes.</t>
   </si>
   <si>
     <t>ehr</t>
@@ -324,7 +381,7 @@
     <t>Electronic Health Records (EHRs)</t>
   </si>
   <si>
-    <t>Electronic health data from electronic health records (Art. 51 1a)</t>
+    <t>Electronic health data from electronic health records (Art. 51 1a).</t>
   </si>
   <si>
     <t>health-factors</t>
@@ -333,7 +390,7 @@
     <t>Health Determinants</t>
   </si>
   <si>
-    <t>Data impacting on health, including socioeconomic, environmental and behavioural determinants (Art. 51 1b)</t>
+    <t>Data impacting health, including socioeconomic, environmental and behavioural determinants (Art. 51 1b).</t>
   </si>
   <si>
     <t>healthcare-resources</t>
@@ -342,7 +399,7 @@
     <t>Aggregated Healthcare Data</t>
   </si>
   <si>
-    <t>Aggregated data on healthcare needs, resources, access, and financing (Art. 51 1c)</t>
+    <t>Aggregated data on healthcare needs, resources, access and financing (Art. 51 1c).</t>
   </si>
   <si>
     <t>pathogen-data</t>
@@ -351,7 +408,7 @@
     <t>Pathogen Data</t>
   </si>
   <si>
-    <t>Data on pathogens impacting on human health (Art. 51 1d)</t>
+    <t>Data on pathogens impacting human health (Art. 51 1d).</t>
   </si>
   <si>
     <t>admin-claims</t>
@@ -360,7 +417,7 @@
     <t>Administrative and Claims Data</t>
   </si>
   <si>
-    <t>Health-related administrative data, including claims and reimbursement data (Art. 51 1e)</t>
+    <t>Health-related administrative data, including claims and reimbursement data (Art. 51 1e).</t>
   </si>
   <si>
     <t>human-genomic</t>
@@ -369,7 +426,7 @@
     <t>Human Genomic Data</t>
   </si>
   <si>
-    <t>Human genetic, epigenomic and genomic data (Art. 51 1f)</t>
+    <t>Human genetic, epigenomic and genomic data (Art. 51 1f).</t>
   </si>
   <si>
     <t>molecular-omics</t>
@@ -378,7 +435,7 @@
     <t>Molecular Omic Data</t>
   </si>
   <si>
-    <t>Other human molecular data, such as proteomic, transcriptomic, metabolomic, lipidomic and other omic data (Art. 51 1g)</t>
+    <t>Other human molecular data, such as proteomic, transcriptomic, metabolomic, lipidomic and other omic data (Art. 51 1g).</t>
   </si>
   <si>
     <t>device-generated-personal</t>
@@ -387,7 +444,7 @@
     <t>Device-Generated Personal Data</t>
   </si>
   <si>
-    <t>Person-generated electronic health data automatically generated by medical devices (Art. 51 1h)</t>
+    <t>Person-generated electronic health data automatically generated by medical devices (Art. 51 1h).</t>
   </si>
   <si>
     <t>wellness-apps</t>
@@ -396,7 +453,7 @@
     <t>Wellness Application Data</t>
   </si>
   <si>
-    <t>Data from wellness applications (Art. 51 1i)</t>
+    <t>Data from wellness applications (Art. 51 1i).</t>
   </si>
   <si>
     <t>professional-status</t>
@@ -405,7 +462,7 @@
     <t>Healthcare Professional Data</t>
   </si>
   <si>
-    <t>Data on the professional status, specialization, and institution of healthcare professionals (Art. 51 1j)</t>
+    <t>Data on the professional status, specialization and institution of healthcare professionals (Art. 51 1j).</t>
   </si>
   <si>
     <t>public-health-registry</t>
@@ -414,7 +471,7 @@
     <t>Public Health Registries</t>
   </si>
   <si>
-    <t>Data from population-wide health data registries (Art. 51 1k)</t>
+    <t>Data from population-wide health data registries (Art. 51 1k).</t>
   </si>
   <si>
     <t>medical-mortality-registry</t>
@@ -423,7 +480,7 @@
     <t>Medical and Mortality Registries</t>
   </si>
   <si>
-    <t>Data from medical registries and mortality registries (Art. 51 1l)</t>
+    <t>Data from medical registries and mortality registries (Art. 51 1l).</t>
   </si>
   <si>
     <t>clinical-trial</t>
@@ -432,7 +489,7 @@
     <t>Clinical Trial Data</t>
   </si>
   <si>
-    <t>Data from clinical trials, clinical studies, and performance studies (Art. 51 1m)</t>
+    <t>Data from clinical trials, clinical studies and performance studies (Art. 51 1m).</t>
   </si>
   <si>
     <t>medical-device-other</t>
@@ -441,7 +498,7 @@
     <t>Other Medical Device Data</t>
   </si>
   <si>
-    <t>Other health data from medical devices (Art. 51 1n)</t>
+    <t>Other health data from medical devices (Art. 51 1n).</t>
   </si>
   <si>
     <t>medicinal-device-registry</t>
@@ -450,7 +507,7 @@
     <t>Medicinal and Device Registries</t>
   </si>
   <si>
-    <t>Data from registries for medicinal products and medical devices (Art. 51 1o)</t>
+    <t>Data from registries for medicinal products and medical devices (Art. 51 1o).</t>
   </si>
   <si>
     <t>research-cohort-survey</t>
@@ -459,7 +516,7 @@
     <t>Research Cohorts and Surveys</t>
   </si>
   <si>
-    <t>Data from research cohorts, questionnaires, and health-related surveys (Art. 51 1p)</t>
+    <t>Data from research cohorts, questionnaires and health-related surveys (Art. 51 1p).</t>
   </si>
   <si>
     <t>biobank</t>
@@ -468,7 +525,7 @@
     <t>Biobank Data</t>
   </si>
   <si>
-    <t>Health data from biobanks and associated databases (Art. 51 1q)</t>
+    <t>Health data from biobanks and associated databases (Art. 51 1q).</t>
   </si>
   <si>
     <t>representative</t>
@@ -477,73 +534,31 @@
     <t>Representative</t>
   </si>
   <si>
-    <t>Data is sufficiently representative of the target population.</t>
+    <t>Data are sufficiently representative of the target population.</t>
   </si>
   <si>
     <t>error-free</t>
   </si>
   <si>
-    <t>Error-free</t>
-  </si>
-  <si>
-    <t>Data is free of errors to the best extent possible.</t>
+    <t>Error-Free</t>
+  </si>
+  <si>
+    <t>Data are free of errors to the best extent possible.</t>
   </si>
   <si>
     <t>Complete</t>
   </si>
   <si>
-    <t>Data is complete regarding the intended purpose.</t>
-  </si>
-  <si>
-    <t>gdpr-art-6-1-a</t>
-  </si>
-  <si>
-    <t>Consent (Art. 6(1)(a))</t>
-  </si>
-  <si>
-    <t>gdpr-art-6-1-b</t>
-  </si>
-  <si>
-    <t>Contract (Art. 6(1)(b))</t>
-  </si>
-  <si>
-    <t>gdpr-art-6-1-d</t>
-  </si>
-  <si>
-    <t>Vital Interests (Art. 6(1)(d))</t>
-  </si>
-  <si>
-    <t>gdpr-art-9-2-a</t>
-  </si>
-  <si>
-    <t>Explicit Consent (Art. 9(2)(a))</t>
-  </si>
-  <si>
-    <t>gdpr-art-9-2-h</t>
-  </si>
-  <si>
-    <t>Health or Social Care (Art. 9(2)(h))</t>
-  </si>
-  <si>
-    <t>gdpr-art-9-2-i</t>
-  </si>
-  <si>
-    <t>Public Health (Art. 9(2)(i))</t>
-  </si>
-  <si>
-    <t>gdpr-art-9-2-j</t>
-  </si>
-  <si>
-    <t>Research (Art. 9(2)(j))</t>
-  </si>
-  <si>
-    <t>eu-ai-database-id</t>
-  </si>
-  <si>
-    <t>EU AI Database Identifier</t>
-  </si>
-  <si>
-    <t>Identifier for an AI system registration in the EU AI database or an equivalent AI system registry.</t>
+    <t>Data are complete with regard to the intended purpose.</t>
+  </si>
+  <si>
+    <t>relevant</t>
+  </si>
+  <si>
+    <t>Relevant</t>
+  </si>
+  <si>
+    <t>Data are relevant for the intended purpose.</t>
   </si>
 </sst>
 </file>
@@ -1064,99 +1079,99 @@
       <c r="C18" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>74</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="D19" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>77</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="D20" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>80</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="D21" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>83</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="D23" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="D23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="D24" t="s" s="2">
-        <v>88</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="D24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="D25" t="s" s="2">
         <v>91</v>
       </c>
+      <c r="D25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
@@ -1168,36 +1183,32 @@
       <c r="C26" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="D26" t="s" s="2">
-        <v>94</v>
-      </c>
+      <c r="D26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B27" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="C27" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>97</v>
-      </c>
+      <c r="D27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B28" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="D28" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="D28" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="29">
@@ -1205,13 +1216,13 @@
         <v>39</v>
       </c>
       <c r="B29" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="D29" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="D29" t="s" s="2">
-        <v>103</v>
       </c>
     </row>
     <row r="30">
@@ -1219,13 +1230,13 @@
         <v>39</v>
       </c>
       <c r="B30" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="D30" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="D30" t="s" s="2">
-        <v>106</v>
       </c>
     </row>
     <row r="31">
@@ -1233,13 +1244,13 @@
         <v>39</v>
       </c>
       <c r="B31" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="D31" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="D31" t="s" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="32">
@@ -1247,13 +1258,13 @@
         <v>39</v>
       </c>
       <c r="B32" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="D32" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="D32" t="s" s="2">
-        <v>112</v>
       </c>
     </row>
     <row r="33">
@@ -1261,13 +1272,13 @@
         <v>39</v>
       </c>
       <c r="B33" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="D33" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="D33" t="s" s="2">
-        <v>115</v>
       </c>
     </row>
     <row r="34">
@@ -1275,13 +1286,13 @@
         <v>39</v>
       </c>
       <c r="B34" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="D34" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="D34" t="s" s="2">
-        <v>118</v>
       </c>
     </row>
     <row r="35">
@@ -1289,13 +1300,13 @@
         <v>39</v>
       </c>
       <c r="B35" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="D35" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="D35" t="s" s="2">
-        <v>121</v>
       </c>
     </row>
     <row r="36">
@@ -1303,13 +1314,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="D36" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="D36" t="s" s="2">
-        <v>124</v>
       </c>
     </row>
     <row r="37">
@@ -1317,13 +1328,13 @@
         <v>39</v>
       </c>
       <c r="B37" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="D37" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="D37" t="s" s="2">
-        <v>127</v>
       </c>
     </row>
     <row r="38">
@@ -1331,13 +1342,13 @@
         <v>39</v>
       </c>
       <c r="B38" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="D38" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="D38" t="s" s="2">
-        <v>130</v>
       </c>
     </row>
     <row r="39">
@@ -1345,13 +1356,13 @@
         <v>39</v>
       </c>
       <c r="B39" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="D39" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="D39" t="s" s="2">
-        <v>133</v>
       </c>
     </row>
     <row r="40">
@@ -1359,13 +1370,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="D40" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="D40" t="s" s="2">
-        <v>136</v>
       </c>
     </row>
     <row r="41">
@@ -1373,13 +1384,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="D41" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="D41" t="s" s="2">
-        <v>139</v>
       </c>
     </row>
     <row r="42">
@@ -1387,13 +1398,13 @@
         <v>39</v>
       </c>
       <c r="B42" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="D42" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="D42" t="s" s="2">
-        <v>142</v>
       </c>
     </row>
     <row r="43">
@@ -1401,13 +1412,13 @@
         <v>39</v>
       </c>
       <c r="B43" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="D43" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="D43" t="s" s="2">
-        <v>145</v>
       </c>
     </row>
     <row r="44">
@@ -1415,13 +1426,13 @@
         <v>39</v>
       </c>
       <c r="B44" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="D44" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="D44" t="s" s="2">
-        <v>148</v>
       </c>
     </row>
     <row r="45">
@@ -1429,13 +1440,13 @@
         <v>39</v>
       </c>
       <c r="B45" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="D45" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="D45" t="s" s="2">
-        <v>151</v>
       </c>
     </row>
     <row r="46">
@@ -1443,13 +1454,13 @@
         <v>39</v>
       </c>
       <c r="B46" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="D46" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="D46" t="s" s="2">
-        <v>154</v>
       </c>
     </row>
     <row r="47">
@@ -1457,13 +1468,13 @@
         <v>39</v>
       </c>
       <c r="B47" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="D47" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="D47" t="s" s="2">
-        <v>157</v>
       </c>
     </row>
     <row r="48">
@@ -1471,13 +1482,13 @@
         <v>39</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="C48" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="D48" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="D48" t="s" s="2">
-        <v>159</v>
       </c>
     </row>
     <row r="49">
@@ -1485,12 +1496,14 @@
         <v>39</v>
       </c>
       <c r="B49" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="C49" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="C49" t="s" s="2">
+      <c r="D49" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="D49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
@@ -1502,80 +1515,92 @@
       <c r="C50" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="D50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>164</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="D51" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="D51" t="s" s="2">
+        <v>167</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="D52" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>170</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="D53" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="D53" t="s" s="2">
+        <v>173</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="D54" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="D54" t="s" s="2">
+        <v>176</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>172</v>
+        <v>31</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="D55" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>178</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
         <v>39</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
